--- a/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
+++ b/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Dropbox (Energy Innovation)\Documents\EPS_Models by Region\India\India_Model\InputData\fuels\BCTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\fuels\BCTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3665FF-58F2-4AAC-932A-8A9D429539EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16ED464C-FC0C-47EF-A2C1-21B0B5CF6166}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="810" windowWidth="14280" windowHeight="14085" xr2:uid="{A875A243-FD0C-4B21-82AE-BAE80D34FF17}"/>
+    <workbookView xWindow="3450" yWindow="435" windowWidth="23955" windowHeight="16500" xr2:uid="{A875A243-FD0C-4B21-82AE-BAE80D34FF17}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BCTR" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -497,121 +497,114 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C1" s="1">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D1" s="1">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F1" s="1">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="H1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="I1" s="1">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="J1" s="1">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="K1" s="1">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="L1" s="1">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="M1" s="1">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="N1" s="1">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="O1" s="1">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="P1" s="1">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="Q1" s="1">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="R1" s="1">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="S1" s="1">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="T1" s="1">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="U1" s="1">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="V1" s="1">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="W1" s="1">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="X1" s="1">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y1" s="1">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="Z1" s="1">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="AA1" s="1">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="AB1" s="1">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="AC1" s="1">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="AD1" s="1">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="AE1" s="1">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="AF1" s="1">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="AG1" s="1">
-        <v>2048</v>
-      </c>
-      <c r="AH1" s="1">
-        <v>2049</v>
-      </c>
-      <c r="AI1" s="1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -711,14 +704,8 @@
       <c r="AG2">
         <v>0</v>
       </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -818,14 +805,8 @@
       <c r="AG3">
         <v>0</v>
       </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -925,14 +906,8 @@
       <c r="AG4">
         <v>0</v>
       </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1032,14 +1007,8 @@
       <c r="AG5">
         <v>0</v>
       </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1139,14 +1108,8 @@
       <c r="AG6">
         <v>0</v>
       </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1246,14 +1209,8 @@
       <c r="AG7">
         <v>0</v>
       </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1353,14 +1310,8 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-      <c r="AH8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -1458,12 +1409,6 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3">
         <v>0</v>
       </c>
     </row>
